--- a/dev/valerio/analysis/metrics_results.xlsx
+++ b/dev/valerio/analysis/metrics_results.xlsx
@@ -240,12 +240,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Benchmarking'!$B$5:$B$9</f>
+              <f>'Benchmarking'!$B$5:$B$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Benchmarking'!$E$5:$E$9</f>
+              <f>'Benchmarking'!$E$5:$E$10</f>
             </numRef>
           </val>
         </ser>
@@ -318,7 +318,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>19</row>
+      <row>24</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="6480000" cy="3600000"/>
@@ -628,7 +628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -644,7 +644,7 @@
     <row r="2" ht="25" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Estudio Experimental Optimizado: Learned Indexes vs Estructuras Tradicionales</t>
+          <t>Estudio de Optimización ML: Learned Indexes ('Antes' vs 'Después')</t>
         </is>
       </c>
     </row>
@@ -688,161 +688,217 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>204.304</v>
+        <v>119.168</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>13.3774</v>
+        <v>19.519</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1.33774</v>
+        <v>1.9519</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>866.119</v>
+        <v>2024.61</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>29.4299</v>
+        <v>44.9956</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Árbol B* + ML (Learned Index)</t>
+          <t>Árbol B* + ML (RMI Baseline - Antes)</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>112.583</v>
+        <v>54.0615</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>5.7782</v>
+        <v>6.3483</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.57782</v>
+        <v>0.63483</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.108294</v>
+        <v>0.387872</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.329081</v>
+        <v>0.622794</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Skip List (Tradicional)</t>
+          <t>★ Árbol B* + ML (RMI Optimizado - Después)</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>549.552</v>
+        <v>50.6559</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>41.704</v>
+        <v>5.1136</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>4.1704</v>
+        <v>0.51136</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>74.64449999999999</v>
+        <v>0.058253</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>8.639699999999999</v>
+        <v>0.241356</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Skip List + ML (Learned)</t>
+          <t>Skip List (Tradicional)</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>509.267</v>
+        <v>422.608</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>35.9052</v>
+        <v>46.1966</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>3.59052</v>
+        <v>4.61966</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>3751.28</v>
+        <v>1697.87</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>61.2477</v>
+        <v>41.2052</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>★ Índice Segmentado ε-Acotado</t>
+          <t>Skip List + ML (Baseline - Antes)</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>32.632</v>
+        <v>407.988</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>6.8499</v>
+        <v>33.5631</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.68499</v>
+        <v>3.35631</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.08356570000000001</v>
+        <v>1384.78</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.289077</v>
-      </c>
-    </row>
-    <row r="10"/>
+        <v>37.2127</v>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>★ Skip List + ML (Optimizado - Después)</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>351.895</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>27.6017</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>2.76017</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>95.3365</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>9.76404</v>
+      </c>
+    </row>
     <row r="11"/>
-    <row r="12">
-      <c r="B12" s="6" t="inlineStr">
+    <row r="12"/>
+    <row r="13">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>Comparativa de Ganancia de Rendimiento (Latencia)</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Arquitectura</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
+    <row r="14"/>
+    <row r="15">
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Arquitectura Comparada</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>Reducción de Latencia (%)</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>Árbol B* + ML vs Árbol B* Tradicional</t>
-        </is>
-      </c>
-      <c r="C15" s="10">
+    <row r="16">
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>Árbol B* + ML (Base) vs Árbol B* Tradicional</t>
+        </is>
+      </c>
+      <c r="C16" s="10">
         <f>(E5-E6)/E5</f>
         <v/>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>Skip List + ML vs Skip List Tradicional</t>
-        </is>
-      </c>
-      <c r="C16" s="10">
-        <f>(E7-E8)/E7</f>
-        <v/>
-      </c>
-    </row>
     <row r="17">
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>★ Índice Segmentado ε-Acotado vs Árbol B* Trad.</t>
+          <t>★ Árbol B* + ML (Optimizado) vs Árbol B* Trad.</t>
         </is>
       </c>
       <c r="C17" s="10">
-        <f>(E5-E9)/E5</f>
+        <f>(E5-E7)/E5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>★ Árbol B* + ML (Optimizado) vs RMI Baseline</t>
+        </is>
+      </c>
+      <c r="C18" s="10">
+        <f>(E6-E7)/E6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>Skip List + ML (Base) vs Skip List Tradicional</t>
+        </is>
+      </c>
+      <c r="C20" s="10">
+        <f>(E8-E9)/E8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>★ Skip List + ML (Optimizada) vs Skip List Trad.</t>
+        </is>
+      </c>
+      <c r="C21" s="10">
+        <f>(E8-E10)/E8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>★ Skip List + ML (Optimizada) vs ML Baseline</t>
+        </is>
+      </c>
+      <c r="C22" s="10">
+        <f>(E9-E10)/E9</f>
         <v/>
       </c>
     </row>
